--- a/public/files/Data_By_Towns_Index/Burlington/Burlington City.xlsx
+++ b/public/files/Data_By_Towns_Index/Burlington/Burlington City.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,571 +425,315 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Unnamed: 0</t>
+          <t>Owner Name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Owner Name</t>
+          <t>Property Location</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Property Location</t>
+          <t>Municipality</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Municipality</t>
+          <t>County</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>State</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Longitude</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>PID</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MEHTA, SURENDER &amp; ANITA</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GUPTA, MONIKA</t>
+          <t>241 MILL RD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>506 YORK ST</t>
+          <t>Burlington City</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Burlington City</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gupta</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>40.0765996</v>
+        <v>-74.86212809999999</v>
       </c>
       <c r="G2" t="n">
-        <v>-74.8543198</v>
+        <v>40.0632738</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ChIJk2V0Y5dOwYkR4CnY54QhJxo</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SHAH, JUNAID</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KUMAR, PRINCE</t>
+          <t>130 W FEDERAL ST</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12 W UNION ST</t>
+          <t>Burlington City</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Burlington City</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kumar</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>40.079033</v>
+        <v>-74.86103659999999</v>
       </c>
       <c r="G3" t="n">
-        <v>-74.85971719999999</v>
+        <v>40.074638</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ChIJLywWSo9OwYkRUhBdkOuM-kA</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DARJI, SUBHASH R &amp; SHANTABEN N</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MEHTA, SURENDER &amp; ANITA</t>
+          <t>417 WASHINGTON AVE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>241 MILL RD</t>
+          <t>Burlington City</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Burlington City</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mehta</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>40.0632738</v>
+        <v>-74.86298379999999</v>
       </c>
       <c r="G4" t="n">
-        <v>-74.86212809999999</v>
+        <v>40.0757539</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ChIJNZk9BYZOwYkRJ3GwN-JVGg0</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PUROHIT, KHUSHALI</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PATEL, AMEET D &amp; URVASHI A</t>
+          <t>308 BROWN ST</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>905 HIGH ST</t>
+          <t>Burlington City</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Burlington City</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>40.067624</v>
+        <v>-74.8660282</v>
       </c>
       <c r="G5" t="n">
-        <v>-74.8534497</v>
+        <v>40.077846</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ChIJIdLH_IZOwYkR9t6rYPshRjk</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PATEL, PARESH KUMAR R &amp; RAMAN B A</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PATEL, AMIT &amp; URVASHI</t>
+          <t>346 BROWN ST</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>812 HIGH ST</t>
+          <t>Burlington City</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Burlington City</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>40.0679356</v>
+        <v>-74.86743559999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-74.85408269999999</v>
+        <v>40.0774251</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ChIJN9i9xYZOwYkRSaS3Xda6Luk</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PATEL, NAINESHKUMAR &amp; VAISHALIBEN</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PATEL, AMIT &amp; URVASHI</t>
+          <t>56 FAWN HOLLOW RD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>818 HIGH ST</t>
+          <t>Burlington City</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Burlington City</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>40.0678345</v>
+        <v>-74.8363409</v>
       </c>
       <c r="G7" t="n">
-        <v>-74.85394409999999</v>
+        <v>40.0720045</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ChIJGe3Ag_lOwYkRq14E7Taqryc</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TRIVEDI, SUNITA</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PATEL, AMIT &amp; URVASHI</t>
+          <t>37 LYNN DR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>910 HIGH ST</t>
+          <t>Burlington City</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Burlington City</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>40.0673572</v>
+        <v>-74.8349769</v>
       </c>
       <c r="G8" t="n">
-        <v>-74.8537961</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>PATEL, AMIT &amp; URVASHI</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>903 HIGH ST</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Burlington City</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>40.0676869</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-74.85339809999999</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>PATEL, HIRENKUMAR B</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>911 ALLISON RD</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Burlington City</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>40.0774819</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-74.84091239999999</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PATEL, KAMLESHKUMAR &amp; JIGNESHKUMAR</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>459 WASHINGTON AVE</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Burlington City</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>40.074656</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-74.86344799999999</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>PATEL, NAINESHKUMAR &amp; VAISHALIBEN</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>56 FAWN HOLLOW RD</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Burlington City</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>40.0720045</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-74.8363409</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>PATEL, PARESH KUMAR R &amp; RAMAN B A</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>346 BROWN ST</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Burlington City</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>40.0774251</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-74.86743559999999</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SHAH, ILYAS M</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>16-18 E BROAD ST</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Burlington City</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Shah</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>40.077644</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-74.857466</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>SHAH, JUNAID</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>130 W FEDERAL ST</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Burlington City</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Shah</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>40.074638</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-74.86103659999999</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>SHAH, JUNAID &amp; RAHIM, ABU</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>22 E BROAD ST</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Burlington City</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Shah</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>40.0776612</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-74.8573734</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>TRIVEDI, SUNITA</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>37 LYNN DR</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Burlington City</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Trivedi</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
         <v>40.0799263</v>
       </c>
-      <c r="G17" t="n">
-        <v>-74.8349769</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>DARJI, SUBHASH R &amp; SHANTABEN N</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>417 WASHINGTON AVE</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Burlington City</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Darji</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>40.0757539</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-74.86298379999999</v>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ChIJh1Nc6VZOwYkRZQ66bWpcL-Q</t>
+        </is>
       </c>
     </row>
   </sheetData>
